--- a/data/trans_dic/IP44C$otros_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$otros_2023-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Adultos que han tenido algún retraso en otros pagos</t>
+          <t>Adultos que han tenido algún retraso en otros pagos (tasa de respuesta: 97,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 7,04</t>
+          <t>0,66; 6,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,74</t>
+          <t>0,52; 3,72</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 8,85</t>
+          <t>3,16; 8,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 8,02</t>
+          <t>2,52; 7,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,55; 7,37</t>
+          <t>3,33; 7,21</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,08; 15,5</t>
+          <t>4,92; 16,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 8,37</t>
+          <t>2,35; 7,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 9,77</t>
+          <t>4,39; 9,95</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,54; 38,85</t>
+          <t>2,46; 39,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 7,27</t>
+          <t>2,43; 6,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,28; 22,98</t>
+          <t>3,46; 22,73</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,66; 22,83</t>
+          <t>4,49; 23,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,54</t>
+          <t>3,05; 5,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 14,04</t>
+          <t>4,29; 15,63</t>
         </is>
       </c>
     </row>
@@ -803,4 +804,454 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido algún retraso en otros pagos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1422</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>358</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1781</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>374; 3739</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2214</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>608; 4387</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>8528</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>8540</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17068</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>4934; 13867</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>4484; 14120</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>11121; 24077</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>14579</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>9487</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>24066</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>8367; 27843</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4777; 15684</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>16391; 37168</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>34552</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>12776</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>47329</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>6630; 105389</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>7319; 20845</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>19745; 129668</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>59082</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>31161</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>90243</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>29306; 151302</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22711; 42436</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>59848; 218197</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP44C$otros_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$otros_2023-Edad-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,56</t>
+          <t>0,66; 6,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>0,0; 3,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,72</t>
+          <t>0,35; 3,58</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 8,89</t>
+          <t>3,25; 8,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,93</t>
+          <t>2,48; 8,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,33; 7,21</t>
+          <t>3,43; 7,32</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,92; 16,37</t>
+          <t>4,86; 16,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,35; 7,7</t>
+          <t>2,53; 8,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 9,95</t>
+          <t>4,31; 10,29</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 39,15</t>
+          <t>2,56; 37,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 6,92</t>
+          <t>2,33; 6,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 22,73</t>
+          <t>3,21; 22,98</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,49; 23,2</t>
+          <t>4,53; 28,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,05; 5,7</t>
+          <t>3,03; 5,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,29; 15,63</t>
+          <t>4,34; 14,28</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>374; 3739</t>
+          <t>376; 3958</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2214</t>
+          <t>0; 1899</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>608; 4387</t>
+          <t>419; 4229</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4934; 13867</t>
+          <t>5068; 13605</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4484; 14120</t>
+          <t>4411; 14756</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11121; 24077</t>
+          <t>11473; 24450</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8367; 27843</t>
+          <t>8266; 28145</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4777; 15684</t>
+          <t>5147; 16912</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16391; 37168</t>
+          <t>16109; 38435</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6630; 105389</t>
+          <t>6885; 102249</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7319; 20845</t>
+          <t>7029; 20499</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19745; 129668</t>
+          <t>18324; 131121</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29306; 151302</t>
+          <t>29523; 187081</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22711; 42436</t>
+          <t>22570; 41086</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>59848; 218197</t>
+          <t>60653; 199332</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$otros_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$otros_2023-Edad-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,12 +549,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,95</t>
+          <t>0,0; 3,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,11</t>
+          <t>0,63; 6,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,58</t>
+          <t>0,37; 3,74</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 8,73</t>
+          <t>2,54; 8,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,29</t>
+          <t>3,19; 8,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,43; 7,32</t>
+          <t>3,55; 7,44</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,86; 16,55</t>
+          <t>2,76; 9,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 8,31</t>
+          <t>4,49; 11,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,31; 10,29</t>
+          <t>4,34; 8,93</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>4,44%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 37,98</t>
+          <t>2,5; 7,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,33; 6,8</t>
+          <t>2,23; 9,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,21; 22,98</t>
+          <t>2,9; 6,88</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>4,84%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 28,69</t>
+          <t>3,13; 5,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,03; 5,52</t>
+          <t>3,9; 7,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,34; 14,28</t>
+          <t>3,76; 6,09</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1422</t>
+          <t>303</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1238</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1781</t>
+          <t>1541</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>376; 3958</t>
+          <t>0; 1760</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1899</t>
+          <t>323; 3561</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>419; 4229</t>
+          <t>382; 3814</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8528</t>
+          <t>7040</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>7906</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17068</t>
+          <t>14946</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5068; 13605</t>
+          <t>3883; 12395</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4411; 14756</t>
+          <t>4567; 12845</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11473; 24450</t>
+          <t>10510; 22059</t>
         </is>
       </c>
     </row>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>15</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>9648</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9487</t>
+          <t>12795</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>24066</t>
+          <t>22444</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8266; 28145</t>
+          <t>5295; 17312</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5147; 16912</t>
+          <t>7694; 20127</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16109; 38435</t>
+          <t>15743; 32400</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>34552</t>
+          <t>12807</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12776</t>
+          <t>11133</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>47329</t>
+          <t>23940</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6885; 102249</t>
+          <t>7220; 21485</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>7029; 20499</t>
+          <t>5597; 22812</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>18324; 131121</t>
+          <t>15634; 37098</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>59082</t>
+          <t>29798</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31161</t>
+          <t>33073</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90243</t>
+          <t>62871</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>29523; 187081</t>
+          <t>21413; 39734</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>22570; 41086</t>
+          <t>24034; 44862</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>60653; 199332</t>
+          <t>48854; 79164</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP44C$otros_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP44C$otros_2023-Edad-trans_dic.xlsx
@@ -17,7 +17,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -98,7 +100,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -111,6 +113,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,341 +485,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Adultos que han tenido algún retraso en otros pagos (tasa de respuesta: 97,81%)</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="n"/>
-      <c r="C1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niña</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" hidden="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>0-2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,5</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,63; 6,9</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,37; 3,74</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>3-7</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>5,51%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>2,54; 8,11</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3,19; 8,96</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3,55; 7,44</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>5,04%</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,18%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n"/>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2,76; 9,04</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4,49; 11,74</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>4,34; 8,93</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>12-15</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4,44%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n"/>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>2,5; 7,45</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>2,23; 9,11</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2,9; 6,88</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>3,13; 5,82</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>3,9; 7,27</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3,76; 6,09</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -879,69 +552,51 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0.00604045121428788</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.02398254634574827</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.01513367945768107</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>303</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1238</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1541</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.006260258253700629</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.003746480330353821</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0; 1760</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>323; 3561</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>382; 3814</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0.03504188375798353</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>0.06899041164662804</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.03744968632592809</v>
       </c>
     </row>
     <row r="7">
@@ -952,69 +607,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0.04604077767854334</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>0.05514128314033664</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.05044472068570569</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>7040</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>7906</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>14946</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0.02539386427648416</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>0.03185366364968245</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.03547071621159405</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>3883; 12395</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>4567; 12845</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>10510; 22059</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.08106242445094865</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.089586207343592</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.07444996911748732</v>
       </c>
     </row>
     <row r="10">
@@ -1025,69 +662,51 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0.05035950904559744</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.07463616116464475</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.06182378966526589</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>9648</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>12795</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>22444</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0.02763526179392959</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>0.04488298293748857</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.04336561008157751</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>5295; 17312</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>7694; 20127</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>15743; 32400</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.09035857049230041</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>0.1174015809357948</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.08925146360508462</v>
       </c>
     </row>
     <row r="13">
@@ -1098,69 +717,51 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.04441166376329812</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>0.04444861345225768</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.04442883975734122</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>12807</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>11133</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>23940</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>0.02503720439088282</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>0.02234535225227155</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.02901350194550607</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>7220; 21485</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>5597; 22812</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>15634; 37098</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>0.07450796202606132</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>0.09107425423651776</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.06884848594215234</v>
       </c>
     </row>
     <row r="16">
@@ -1171,69 +772,51 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>0.04362333402280392</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.05361046096996077</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.04836267915267855</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>29798</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>33073</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>62871</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>0.03134814290776823</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>0.03895843596629513</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.03758021569283367</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>21413; 39734</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>24034; 44862</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>48854; 79164</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.05816785064211902</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.07272110391606745</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.06089613529880177</v>
       </c>
     </row>
     <row r="19">
@@ -1254,4 +837,449 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Adultos que han tenido algún retraso en otros pagos (tasa de respuesta: 97,81%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>303</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>1238</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>323</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n"/>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1760</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>3561</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>3814</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>16</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>7040</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>7906</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>14946</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n"/>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>3883</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>4567</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>10510</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>12395</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>12845</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>22059</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n"/>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>9648</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>12795</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>22444</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>5295</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>7694</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>15743</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>17312</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>20127</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>32400</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>12807</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>11133</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>23940</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>7220</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>5597</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>15634</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>21485</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>22812</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>37098</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>29798</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>33073</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>62871</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>21413</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>24034</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>48854</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>39734</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>44862</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>79164</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A4:A7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="A12:A15"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A16:A19"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>